--- a/output/北塩原村_広域連携_RedTeam再レビュー.xlsx
+++ b/output/北塩原村_広域連携_RedTeam再レビュー.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -578,12 +578,19 @@
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>7. レビューが挙げた参照元15件は、当方の環境からは取得できない（組織のネットワーク方針により接続が403で遮断される）。相手方の計画・県資料に関する本書の記述は、出所がレビューの記述である。計画本文に相手方の数値や合意を書く箇所には【村へ確認】を添えた。</t>
+          <t>7. 参照元は、令和8年10月10日に追加で受領したエビデンスパック（E01〜E14）により09シートに整理した。パックに収められているのは公式URL・資料名・公表主体・確認日・確認した根拠事項を整理したメモであり、原本そのものではない。当方の環境からは原典を取得できない（組織のネットワーク方針により接続が403で遮断される）ため、相手方の計画・県資料に関する本書の記述は出所がこのパックである。計画本文に相手方の数値や合意を書く箇所には【村へ確認】を添えた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>8. パックを読んで当方の記録を3点直した。①基幹相談支援センターの根拠は令和6年度の県協議会資料であり、当初「令和7年度」としていたのは誤りであった（E03）。②磐梯町は協議の場だけでなく、医療的ケア児等コーディネーターも「1人（圏域）」と目標に置いている（E06）。県の修了者一覧には磐梯町保健福祉センターと地域生活支援センターいなわしろの所属者が載っており（E11）、県は配置の状況を各市町村の窓口に確かめるよう求めている（E10）。二重計上の懸念はより具体的になった。③E01の公式URLが配信用のホスト名で示されていたため、成果物には安定したページの方を載せた。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
@@ -591,6 +598,7 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
@@ -604,25 +612,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>レビューが挙げた参照元</t>
+          <t>参照元（受領したエビデンスパックによる）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>いずれも当方の環境からは取得できない（組織のネットワーク方針により接続が403で遮断される。再試行はしない）。本書の記述のうち相手方の計画・県資料に関する部分は、出所がレビューの記述である。</t>
+          <t>令和8年10月10日に受領した「北塩原村_広域連携_参照エビデンス」（source/レビュー_20261010/広域連携_参照エビデンス）を読んだもの。いずれも当方の環境からは原典を取得できない（組織のネットワーク方針により接続が403で遮断される。再試行はしない）。本書の記述のうち相手方の計画・県資料に関する部分は、出所がこのパックの記述である。</t>
         </is>
       </c>
     </row>
@@ -639,6 +651,26 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>公表主体</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>確認した根拠事項</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>留意事項</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>確認日</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>URL（当方は未取得）</t>
         </is>
       </c>
@@ -646,7 +678,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -656,22 +688,64 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>https://www.pref.fukushima.lg.jp/sec/21035a/syougaijihukusikeikakusakutei.html</t>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>県が第7期障がい福祉計画・第3期障がい児福祉計画を策定。市町村計画の広域・圏域整合、サービス基盤、相談支援、障がい児支援の基礎資料。</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>県第8期・第4期の最終公表後に北塩原村計画との再照合が必要。</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.pref.fukushima.lg.jp/sec/21035a/syougaijihukusikeikakusakutei.html
+（関連）https://www.pref.fukushima.lg.jp/uploaded/attachment/625631.pdf
+※パックの公式URLは配信用のホスト名であったため、安定したページに差し替えた（パックの値 https://g5htx4cdn.pref.fukushima.lg.jp/sec/21035c/keikaku.html）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福島県 会津地域保健医療福祉推進計画</t>
+          <t>会津地域保健医療福祉推進計画</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>福島県 会津保健福祉事務所</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>令和12年度までの会津地域の保健・医療・福祉計画。会津地域での医療・福祉連携、相談支援、地域生活支援、社会資源・人材の地域課題を確認する基礎資料。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>北塩原村の医療連携・精神地域包括ケアは会津北部4町村より広い圏域での整合が必要。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>https://www.pref.fukushima.lg.jp/sec/21140a/aidukeikaku.html</t>
         </is>
@@ -680,58 +754,120 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>令和7年度 福島県会津地域保健医療福祉協議会資料</t>
+          <t>会津地域保健医療福祉協議会資料（基幹相談支援センター等）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>https://wwwcms.pref.fukushima.jp/uploaded/attachment/738832.pdf</t>
+          <t>福島県 会津保健福祉事務所</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>令和6年度資料では、地域生活支援拠点等の運営支援に係る勉強会等への参加が会津北部4回、基幹相談支援センター設置支援に係る勉強会等への参加も会津北部4回と記載。</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>会津北部の基幹相談支援センターを設置済みと断定せず、現状・R9以降の設置予定を確認する根拠。</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pref.fukushima.lg.jp/uploaded/attachment/681999.pdf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>地域生活支援センターいなわしろ（福島県社会福祉事業団）</t>
+          <t>地域生活支援センターいなわしろ</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://www.fukushima-sj.jp/facility/chisei/</t>
+          <t>社会福祉法人 福島県社会福祉事業団</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>委託相談支援の実施地域として猪苗代町・磐梯町・北塩原村・湯川村を明示。地域移行支援、会津北部地域生活支援拠点事業も実施。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>4町村の拠点・相談・地域移行・コーディネートの中核的広域資源。</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fukushima-sj.jp/facility/chisei/
+（関連）https://www.fukushima-sj.jp/pdf/facility/pamphlet-chisei-inawashiro.pdf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>北塩原村 第7期計画・関連資料</t>
+          <t>北塩原村 現行計画関連（基幹相談広域設置等）</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>https://www.vill.kitashiobara.fukushima.jp/uploaded/attachment/3388.pdf</t>
+          <t>北塩原村</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>基幹相談支援センターについて、猪苗代町・磐梯町・湯川村・北塩原村で広域設置を検討し、令和8年度末までの設置を目標としていたことを確認。</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>前回目標と現状の差を次回委員会で評価する必要。</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.vill.kitashiobara.fukushima.jp/uploaded/attachment/3379.pdf
+（関連）https://www.vill.kitashiobara.fukushima.jp/uploaded/attachment/3388.pdf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -740,6 +876,26 @@
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>磐梯町</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>医療的ケア児支援の協議の場を1か所（圏域）、医療的ケア児等コーディネーターを1人（圏域）とする目標を確認。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>北塩原村の『4町村共同』記載と、磐梯町の『圏域』表記が同一の連携単位か要確認。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>https://www.town.bandai.fukushima.jp/uploaded/attachment/6244.pdf</t>
         </is>
@@ -748,15 +904,35 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>磐梯町 医療的ケア児等コーディネーター配置事業実施要綱（令和8年4月1日施行）</t>
+          <t>磐梯町 医療的ケア児等コーディネーター配置事業実施要綱</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>磐梯町</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>令和8年4月1日施行。磐梯町を実施主体とし、サービス情報提供、保健・医療・福祉・子育て・教育等の調整、地域資源開拓、協議の場への参画等をコーディネーター業務として規定。</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>北塩原村計画の『コーディネーター1人』との役割・区域の重複確認が必要。</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>https://www.town.bandai.fukushima.jp/data/reiki_int/reiki_honbun/c545RG00001049.html</t>
         </is>
@@ -765,15 +941,35 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湯川村 第4期障がい者計画・第7期障がい福祉計画・第3期障がい児福祉計画</t>
+          <t>湯川村 第4期障がい者計画</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>湯川村</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>会津北部圏域で地域生活支援拠点を整備済みとし、コーディネーター体制、緊急時連絡体制、運用検証、強度行動障害のニーズ把握等を位置付け。</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>4町村拠点のKPI定義・実績様式の共通化に用いる比較資料。</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>https://www.vill.yugawa.fukushima.jp/uploaded/attachment/1415.pdf</t>
         </is>
@@ -782,24 +978,45 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>猪苗代町 各種計画（本文の数値目標は未取得）</t>
+          <t>猪苗代町 各種計画／保健福祉課</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>https://www.town.inawashiro.fukushima.jp/life/5/23/99/</t>
+          <t>猪苗代町</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>猪苗代町公式サイトで障がい福祉関係計画・障がい児者相談等の公表を確認。地域生活支援センターいなわしろが町内に立地。</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>今回の取得では猪苗代町現行計画本文の個別KPIまで確認できなかったため、次回原典照合が必要。</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.town.inawashiro.fukushima.jp/life/5/23/99/
+（関連）https://www.town.inawashiro.fukushima.jp/soshiki/5/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -808,6 +1025,26 @@
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>医療的ケア児等コーディネーター養成研修修了者情報を公表。県は配置状況について各市町村担当窓口への確認を求めている。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>『研修修了者＝自治体の配置コーディネーター』ではないことを確認する根拠。</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>https://www.pref.fukushima.lg.jp/sec/21035a/ikeaji.html</t>
         </is>
@@ -816,15 +1053,35 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>福島県 医療的ケア児等コーディネーター養成研修修了者一覧</t>
+          <t>福島県 医療的ケア児等コーディネーター養成研修修了者リスト</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>会津圏域の修了者として、磐梯町保健福祉センター及び地域生活支援センターいなわしろ所属者等を確認。</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>修了者の所属と、各自治体の正式な配置・委託関係は別途確認が必要。</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>https://www.pref.fukushima.lg.jp/uploaded/attachment/721405.pdf</t>
         </is>
@@ -833,75 +1090,128 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福島県 障害児通所支援事業所一覧（令和7年4月1日現在）</t>
+          <t>福島県 障害児支援施設・事業所に関する県資料</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://www.pref.fukushima.lg.jp/uploaded/attachment/695266.pdf</t>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>会津若松市内の児童発達支援センター『ゆめみっこ』『たんぽぽ園』を確認。会津圏域資料では児童発達支援、放課後等デイ、保育所等訪問、児童利用可能な短期入所等の配置状況を確認。</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>北塩原村計画の『近隣市町村のセンター』を具体化する根拠。</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pref.fukushima.lg.jp/uploaded/life/801223_2313078_misc.pdf
+（関連）https://www.pref.fukushima.lg.jp/uploaded/life/366448_2139243_misc.pdf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>会津若松市 児童発達支援センター等</t>
+          <t>福島県医療的ケア児支援センター</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>https://www.city.aizuwakamatsu.fukushima.jp/docs/2023072000011/</t>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>県内の医療的ケア児等支援、コーディネーター研修・フォローアップ、人材間の情報共有を行う県レベルの専門支援基盤。</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>北塩原村の医療連携を『村・会津圏域・県』の3層で整理する根拠。</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pref.fukushima.lg.jp/sec/21810a/iryoutekikeasiensenta.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>E14</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>福島県医療的ケア児支援センター</t>
+          <t>会津権利擁護・成年後見センター関係</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://www.pref.fukushima.lg.jp/sec/21810a/iryoutekikeasiensenta.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>E-15</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>会津権利擁護・成年後見センター</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>https://www.aizu-anshin-net.org/</t>
+          <t>会津若松市／会津権利擁護・成年後見センター</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>会津圏域11市町村（北塩原村、猪苗代町、磐梯町、湯川村を含む）が参加するセンターであることを会津若松市公式ページで確認。</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>成年後見・権利擁護KPIを障がい計画と介護計画で共通化する根拠。</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kw.city.aizuwakamatsu.fukushima.jp/docs/2025053000034/
+（関連）https://www.aizu-anshin-net.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>パックに収められているのは、公式URL・資料名・公表主体・確認日・確認した根拠事項を整理したメモであり、原本のPDF・HTMLそのものではありません。村へ正式に提出する際は、各公式URLから原本を取得し、同じ番号で添えると追跡しやすくなります。猪苗代町（E09）は現行計画の本文まで確認できておらず、個別の目標値は推測せず要原典確認としています。なお、レビュー本体が挙げていた会津若松市の児童発達支援センター等のページはパックに含まれていません。児童発達支援センターの機能の確認（Ｍ-102）では、県の事業所一覧（E12）を根拠として用いています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1238,7 +1548,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>A 設置済みとして扱わないこと。県協議会資料では設置支援・勉強会（会津北部4回）が継続している</t>
+          <t>A 設置済みとして扱わないこと。県の会津地域保健医療福祉協議会の令和6年度資料では、基幹相談支援センター設置支援に係る勉強会等への参加が会津北部4回、地域生活支援拠点等の運営支援に係る勉強会等への参加も会津北部4回と記載されている（E03）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1265,7 +1575,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>A 磐梯町・湯川村の現行計画は「圏域1か所」としており、「圏域」＝会津北部4町村であることを示す共通の根拠は確認できない</t>
+          <t>A 磐梯町・湯川村の現行計画は「圏域1カ所」としており、磐梯町はコーディネーターも「1人（圏域）」と置いている（E06）。「圏域」＝会津北部4町村であることを示す共通の根拠は確認できない</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1292,7 +1602,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>A 研修修了者と自治体の配置コーディネーターは別である。磐梯町は令和8年4月から独自の配置事業を制度化しており、同じ人を双方が数えると二重計上になる</t>
+          <t>A 研修修了者と自治体の配置コーディネーターは別である。磐梯町は第7期計画でコーディネーターを「1人（圏域）」と目標に置き、令和8年4月から独自の配置事業を制度化している（E06・E07）。県の修了者一覧には磐梯町保健福祉センター及び地域生活支援センターいなわしろの所属者が載っており（E11）、県は配置の状況を各市町村の窓口に確かめるよう求めている（E10）。同じ人を双方が数えると二重計上になる</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -2760,7 +3070,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>貴町村が配置する者は誰か、本村が数える者と同一人か、独自の配置事業との役割分担</t>
+          <t>貴町村が配置する者の所属と担当区域、本村が数える者と同一人か、独自の配置事業（磐梯町は令和８年４月施行の要綱）との役割分担。計画上の目標値を「圏域１人」としている場合、その圏域はどの範囲か</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2907,7 +3217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3030,7 +3340,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>本計画では医療的ケア児等コーディネーター１人を令和８年度に配置したものとして記載しています。この１人について、次をご教示ください。①氏名は不要ですので、所属（村、相談支援事業所、地域生活支援センターいなわしろ等の別）。②配置又は委託の主体（本村か、４町村共同か）。③担当する区域（本村のみか、４町村か）。④根拠（要綱等の有無）。⑤対象（医療的ケア児のみか、成人の医療的ケア者を含むか）。⑥令和７年度・令和８年度の支援ケース数と個別支援会議の回数。県の養成研修を修了していることと、市町村が配置する者として位置づけられていることは別であり、近隣町村が独自に配置する方と同一人である場合、両方の計画で数えると実際より多く見えるためです。</t>
+          <t>本計画では医療的ケア児等コーディネーター１人を令和８年度に配置したものとして記載しています。この１人について、次をご教示ください。①氏名は不要ですので、所属（村、相談支援事業所、地域生活支援センターいなわしろ等の別）。②配置又は委託の主体（本村か、４町村共同か）。③担当する区域（本村のみか、４町村か）。④根拠（要綱等の有無）。⑤対象（医療的ケア児のみか、成人の医療的ケア者を含むか）。⑥令和７年度・令和８年度の支援ケース数と個別支援会議の回数。県の養成研修を修了していることと、市町村が配置する者として位置づけられていることは別であり、県も配置の状況は各市町村の窓口に確かめるよう求めています。県の修了者の一覧には、磐梯町保健福祉センター及び地域生活支援センターいなわしろに所属する方が載っています。磐梯町は第７期計画でコーディネーターを「１人（圏域）」と目標に置き、令和８年４月から独自の配置事業を要綱で定めています。同じ方を本村と磐梯町の双方が数えると、会津北部４町村の合計が実際より多く見えるためです。</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -3061,6 +3371,33 @@
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>令和８年12月12日（金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Ｍ-102</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>村</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>児童発達支援センターの４つの中核機能の接続先</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>本計画の第４章２（４）では、本村に児童発達支援センターがないため、会津障がい保健福祉圏域のセンター等と連携して４つの中核機能を確保することとしています。県の事業所一覧によれば、会津障がい保健福祉圏域の児童発達支援センターは会津若松市内にあり、近隣の町村にあるのは児童発達支援事業所又は放課後等デイサービス事業所であって区分が異なります。次をご確認ください。①本村の児童が実際に相談・支援を受けている施設の名称。②その施設から、㋐高度な専門性に基づく発達支援・家族支援、㋑村内の障がい児通所支援事業所へのスーパーバイズ・コンサルテーション、㋒インクルージョン推進の中核、㋓発達支援の入口としての相談、のどの機能を受けられるか。③村内の保育所、幼稚園及び学校への助言や保育所等訪問支援の対象に本村が含まれるか。④冬季の積雪期も含めて通所・訪問が可能か。接続先が特定できない場合、「圏域で確保する」という記述の裏づけが取れません。</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>令和８年12月12日（金）</t>
         </is>

--- a/output/北塩原村_広域連携_RedTeam再レビュー.xlsx
+++ b/output/北塩原村_広域連携_RedTeam再レビュー.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_照会" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_退けた指摘" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_参照元" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_基幹相談支援センター" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -585,13 +586,21 @@
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>8. パックを読んで当方の記録を3点直した。①基幹相談支援センターの根拠は令和6年度の県協議会資料であり、当初「令和7年度」としていたのは誤りであった（E03）。②磐梯町は協議の場だけでなく、医療的ケア児等コーディネーターも「1人（圏域）」と目標に置いている（E06）。県の修了者一覧には磐梯町保健福祉センターと地域生活支援センターいなわしろの所属者が載っており（E11）、県は配置の状況を各市町村の窓口に確かめるよう求めている（E10）。二重計上の懸念はより具体的になった。③E01の公式URLが配信用のホスト名で示されていたため、成果物には安定したページの方を載せた。</t>
+          <t>8. 基幹相談支援センターについては、国の一覧の現物を受領したため、レビューの記述ではなく原典で裏づけられるようになった（ＫＯ-5）。令和7年4月1日時点で、会津障がい保健福祉圏域13市町村のうち8市町村が基幹相談支援センターを持ち、その数は3カ所である。本村・西会津町・磐梯町・猪苗代町・湯川村の5町村には無い。さらに、会津西部基幹相談支援センターは会津美里町を主たる設置主体とする6町村の共同設置であり、小規模な町村が共同で設置した例が同じ圏域の中に既にある。本村が目指す会津北部4町村での広域設置には先例があるということであり、委員会にはこの形で示す。Ｍ-98も「設置済みか」ではなく「この例に倣えるか」に改めた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>9. パックを読んで当方の記録を3点直した。①基幹相談支援センターの根拠は令和6年度の県協議会資料であり、当初「令和7年度」としていたのは誤りであった（E03）。②磐梯町は協議の場だけでなく、医療的ケア児等コーディネーターも「1人（圏域）」と目標に置いている（E06）。県の修了者一覧には磐梯町保健福祉センターと地域生活支援センターいなわしろの所属者が載っており（E11）、県は配置の状況を各市町村の窓口に確かめるよう求めている（E10）。二重計上の懸念はより具体的になった。③E01の公式URLが配信用のホスト名で示されていたため、成果物には安定したページの方を載せた。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
@@ -1217,6 +1226,268 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>会津障がい保健福祉圏域の基幹相談支援センター（令和７年４月１日時点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>厚生労働省「基幹相談支援センター一覧（令和７年４月１日時点）」（001698042.pdf）の現物から数えたもの。本書の参照元のうち、当方が原典を手にしているのはこの一覧だけである。数は手で書かず、生成のたびに一覧から数え直す。全国の主たる設置の行は1049件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>市町村</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>基幹相談支援センター</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>設置の形</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>共同設置の市町村</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>会津若松市</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>会津若松市障がい者総合相談窓口</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>単独</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>喜多方市</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>基幹相談支援センターウィズピア</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>単独</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>会津美里町</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>会津西部基幹相談支援センター</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>共同（6町村）</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>会津坂下町、柳津町、三島町、金山町、昭和村</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>設置がない市町村</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>基幹相談支援センター</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>設置の形</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>北塩原村</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>本計画の会津北部４町村に含まれる</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>西会津町</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>磐梯町</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>本計画の会津北部４町村に含まれる</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>猪苗代町</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>本計画の会津北部４町村に含まれる</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>湯川村</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>本計画の会津北部４町村に含まれる</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>会津障がい保健福祉圏域13市町村のうち、8市町村が基幹相談支援センターを持ち、その数は3カ所です。会津西部基幹相談支援センターは、会津美里町を主たる設置主体とし、会津坂下町、柳津町、三島町、金山町及び昭和村と共同で設置したものです。小規模な町村が共同で設置した例が同じ圏域の中に既にあり、本村が目指す会津北部４町村での広域設置の参考になります。この事実は正本 第４章２（６）に入れました（ＫＯ-5）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1553,7 +1824,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>維持。正本は既に未設置と明記しており、レビューが懸念した「設置済み扱い」にはなっていない。正式合意の有無と設置予定年度のみＭ-98で確かめる</t>
+          <t>維持したうえで、国の一覧の現物で裏づけた（ＫＯ-5）。令和7年4月1日時点で、会津障がい保健福祉圏域13市町村のうち8市町村が基幹相談支援センターを持ち、その数は3カ所。北塩原村・西会津町・磐梯町・猪苗代町・湯川村の5町村には無い。会津西部基幹相談支援センターは会津美里町を主たる設置主体とする6町村の共同設置であり、圏域内に広域設置の先例がある。Ｍ-98では、設置済みかどうかではなく、令和8年度の協議の状況と、この例に倣えるかを尋ねる</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2721,6 +2992,142 @@
       <c r="C33" s="4" t="inlineStr">
         <is>
           <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できるかを県（会津保健福祉事務所）及び当該事業所に確認してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ＫＯ-5</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>国が公表した一覧によれば、令和７年４月１日時点で、会津障がい保健福祉圏域の13市町村のうち８市町村が基幹相談支援センターを持っており、その数は３カ所です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ＫＯ-5</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>基幹相談支援センター ／ 設置の形 ／ 対象となる市町村</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ＫＯ-5</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>会津若松市障がい者総合相談窓口 ／ 単独 ／ 会津若松市</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ＫＯ-5</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>基幹相談支援センターウィズピア ／ 単独 ／ 喜多方市</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ＫＯ-5</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>会津西部基幹相談支援センター ／ 共同（６町村） ／ 会津美里町（主たる設置主体）、会津坂下町、柳津町、三島町、金山町、昭和村</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ＫＯ-5</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>本村、西会津町、磐梯町、猪苗代町、湯川村の５町村には、基幹相談支援センターがありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>ＫＯ-5</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>このうち会津西部基幹相談支援センターは、一つの町が主たる設置主体となり、近隣の町村と共同で設置したものです。同じ圏域の中に、小規模な町村が共同で設置した例が既にあります。会津北部４町村での広域設置に向けては、主たる設置主体となる町村、設置の場所、委託先、主任相談支援専門員等の人員及び費用の分担を決める必要があります。この例を参考にしながら、県（会津保健福祉事務所）が未設置の市町村に対して行う相談支援アドバイザーによる支援を活用して協議を進めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ＫＯ-5</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に倣えるかを確認してください。</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3693,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>本計画では、地域生活支援拠点、基幹相談支援センター、医療的ケア児等支援、インクルージョン推進及び強度行動障害支援を、猪苗代町、磐梯町及び湯川村との広域で確保することとしています。しかしながら、本村の計画に「広域で行う」と書いても、相手方の計画で同じ連携単位、同じ会議体、同じ数え方になっていなければ、広域で確保したことになりません。別紙の共同確認票（16項目）により、３町村へご照会いただきたくお願いいたします。とくに次の５点は、本計画の成果目標の書き方に直に関わります。①令和９〜11年度も地域生活支援拠点を４町村共同で継続するか。②基幹相談支援センターの４町村共同設置について正式な合意があるか、設置の予定年度はいつか。③医療的ケア児等支援の協議の場について、磐梯町及び湯川村の現行計画にある「圏域１か所」の圏域が、会津北部の４町村を指すのか会津障がい保健福祉圏域を指すのか。④医療的ケア児等コーディネーターについて、各町村が数える方が同一人でないか。⑤インクルージョン推進のための協議の場を令和９〜11年度の共通の目標とできるか。</t>
+          <t>本計画では、地域生活支援拠点、基幹相談支援センター、医療的ケア児等支援、インクルージョン推進及び強度行動障害支援を、猪苗代町、磐梯町及び湯川村との広域で確保することとしています。しかしながら、本村の計画に「広域で行う」と書いても、相手方の計画で同じ連携単位、同じ会議体、同じ数え方になっていなければ、広域で確保したことになりません。別紙の共同確認票（16項目）により、３町村へご照会いただきたくお願いいたします。とくに次の５点は、本計画の成果目標の書き方に直に関わります。①令和９〜11年度も地域生活支援拠点を４町村共同で継続するか。②基幹相談支援センターについて、令和８年度の協議の状況と、会津西部基幹相談支援センター（会津美里町を主たる設置主体とし、会津坂下町、柳津町、三島町、金山町及び昭和村と共同で設置したもの）の例に倣えるか。主たる設置主体となる町村、設置の場所、委託先、主任相談支援専門員等の人員及び費用の分担について合意の見込みがあるか。なお、国の一覧によれば令和７年４月１日時点で４町村のいずれにも設置はありません。③医療的ケア児等支援の協議の場について、磐梯町及び湯川村の現行計画にある「圏域１か所」の圏域が、会津北部の４町村を指すのか会津障がい保健福祉圏域を指すのか。④医療的ケア児等コーディネーターについて、各町村が数える方が同一人でないか。⑤インクルージョン推進のための協議の場を令和９〜11年度の共通の目標とできるか。</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">

--- a/output/北塩原村_広域連携_RedTeam再レビュー.xlsx
+++ b/output/北塩原村_広域連携_RedTeam再レビュー.xlsx
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>次の事項について、県へご照会いただきたくお願いいたします。当方からは県の資料に当たることができないため、いずれも計画の記述の裏づけに要るものです。①第８期福島県障がい福祉計画・第４期福島県障がい児福祉計画の公表の予定（本計画の基盤整備量は県の算定値を勘案して定めます）。②精神病床の長期入院者の地域移行に伴う基盤整備量の県の算定値と、会津障がい保健福祉圏域での考え方、市町村が自らの値を設定する方法。③会津圏域の医療型短期入所の最新の指定の状況（県の圏域資料では令和５年４月１日現在０か所とされています）。④主に重症心身障がい児を支援する事業所の最新の指定の状況。⑤会津北部における基幹相談支援センターの設置支援の進捗。⑥医療的ケア児等支援のための協議の場について、県が適切と考える圏域の単位。⑦会津圏域の就労選択支援事業所の整備の状況。⑧福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称・連絡先・利用の手順。</t>
+          <t>次の事項について、県へご照会いただきたくお願いいたします。当方からは県の資料に当たることができないため、いずれも計画の記述の裏づけに要るものです。①第８期福島県障がい福祉計画・第４期福島県障がい児福祉計画の公表の予定（本計画の基盤整備量は県の算定値を勘案して定めます）。②精神病床の長期入院者の地域移行に伴う基盤整備量の県の算定値と、会津障がい保健福祉圏域での考え方、市町村が自らの値を設定する方法。③会津圏域の医療型短期入所の最新の指定の状況（県の圏域資料では令和５年４月１日現在０か所とされています）。④主に重症心身障がい児を支援する事業所の最新の指定の状況。⑤会津北部における基幹相談支援センターの設置支援の進捗。⑥医療的ケア児等支援のための協議の場について、県が適切と考える圏域の単位。⑦会津圏域の就労選択支援事業所の整備の状況。⑧福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称・連絡先・利用の手順。⑨高次脳機能障害者支援センター及び支援コーディネーターの設置の状況と、高次脳機能障害者支援地域協議会の有無。あわせて会津圏域における相談の窓口と、診断・治療・リハビリテーションを行う専門的な医療機関。⑩強度行動障害の「広域的支援人材」の配置の状況と、本村の住民に係る事案で助言や集中的支援を受ける手順。⑪令和９年度から始まる強度行動障害の「中核的人材」の養成研修の実施の予定。⑫福島県発達障害者支援センターの会津圏域における相談の導線と、発達障がいの診断に係る初めての受診までの待ち時間の状況。⑬障がい福祉の分野の人材確保・生産性向上について県が設けるサポートセンター（ワンストップ窓口）の設置の状況と、市町村が利用する方法。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">

--- a/output/北塩原村_広域連携_RedTeam再レビュー.xlsx
+++ b/output/北塩原村_広域連携_RedTeam再レビュー.xlsx
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>上の表は、村内で受けられる医療と圏域の市町に出向いて受ける医療の２つを扱っています。これに加えて、県が持つ専門の支援があります。医療的ケアを必要とする方については福島県医療的ケア児支援センターが相談と地域支援を担い、高次脳機能障害のある方については県が専門の相談の窓口を置いています。村内の診療所、圏域の医療機関、県の専門支援の三つの層を分けて考え、本人や家族が自分でたどり着けない場合には、村保健福祉課又は相談支援専門員が県の窓口までつなぎます。</t>
+          <t>上の表は、村内で受けられる医療と圏域の市町に出向いて受ける医療の２つを扱っています。これに加えて、県が持つ専門の支援があります。医療的ケアを必要とする方については福島県医療的ケア児支援センターが相談と地域支援を担い、高次脳機能障害のある方については県が専門の相談の窓口を置いています。なお、医療的ケア児及びその家族に対する支援に関する法律の改正（令和８年法律第77号。令和９年４月１日施行）により、このセンターの名称は「医療的ケア児等支援センター」に改められます。施行の日は本計画の期間の初日に当たるため、本計画期間においては改称後の名称で扱います。村内の診療所、圏域の医療機関、県の専門支援の三つの層を分けて考え、本人や家族が自分でたどり着けない場合には、村保健福祉課又は相談支援専門員が県の窓口までつなぎます。</t>
         </is>
       </c>
     </row>
